--- a/clip_trait_similarities_full_float.xlsx
+++ b/clip_trait_similarities_full_float.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B94"/>
+  <dimension ref="A1:B151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -431,1116 +431,1800 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>a artificial person</t>
+          <t>a impractical person</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.061366282403</t>
+          <t>0.048171058297</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>a superficial person</t>
+          <t>a simple person</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.056110765785</t>
+          <t>0.032227523625</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>a one-dimensional person</t>
+          <t>a confused person</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.045606330037</t>
+          <t>0.031748224050</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>a lazy person</t>
+          <t>a unreflective person</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.043037537485</t>
+          <t>0.030709752813</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>a ridiculous person</t>
+          <t>a artificial person</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.033578328788</t>
+          <t>0.025505160913</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>a bland person</t>
+          <t>a repressed person</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0.031016400084</t>
+          <t>0.024827096611</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>a scornful person</t>
+          <t>a superficial person</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0.027854088694</t>
+          <t>0.023320853710</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>a unimpressive person</t>
+          <t>a unconvincing person</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0.024604789913</t>
+          <t>0.022361282259</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>a charmless person</t>
+          <t>a shameless person</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0.023985130712</t>
+          <t>0.022044518963</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>a criminal person</t>
+          <t>a pretentious person</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0.022546561435</t>
+          <t>0.021289356053</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>a pompous person</t>
+          <t>a one-dimensional person</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0.021488325670</t>
+          <t>0.018955018371</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>a careless person</t>
+          <t>a lazy person</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0.019757233560</t>
+          <t>0.017887335271</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>a uncooperative person</t>
+          <t>a unambitious person</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0.018977131695</t>
+          <t>0.016491476446</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>a obnoxious person</t>
+          <t>a naive person</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0.018238887191</t>
+          <t>0.016361610964</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>a prejudiced person</t>
+          <t>a troublesome person</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0.017591327429</t>
+          <t>0.016333609819</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>a tactless person</t>
+          <t>a egocentric person</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0.017236905172</t>
+          <t>0.016049310565</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>a unhealthy person</t>
+          <t>a rowdy person</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0.016904221848</t>
+          <t>0.015839988366</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>a dull person</t>
+          <t>a oppressed person</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0.016683971509</t>
+          <t>0.015666559339</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>a unfriendly person</t>
+          <t>a disorganised person</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0.015936728567</t>
+          <t>0.015361781232</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>a tasteless person</t>
+          <t>a vulnerable person</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0.015499174595</t>
+          <t>0.015188256279</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>a cold person</t>
+          <t>a ridiculous person</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0.015054698102</t>
+          <t>0.013955883682</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>a dirty person</t>
+          <t>a disorderly person</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0.014734397642</t>
+          <t>0.013698670082</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>a resentful person</t>
+          <t>a absentminded person</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0.014148596674</t>
+          <t>0.013357726857</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>a stupid person</t>
+          <t>a bland person</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0.014126431197</t>
+          <t>0.012891089544</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>a disturbing person</t>
+          <t>a short-sighted person</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0.013840946369</t>
+          <t>0.012640427798</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>a disrespectful person</t>
+          <t>a scornful person</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0.013299339451</t>
+          <t>0.011576764286</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>a gloomy person</t>
+          <t>a unimaginative person</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0.012536539696</t>
+          <t>0.010724824853</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>a remorseless person</t>
+          <t>a coarse person</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0.012167854235</t>
+          <t>0.010686476715</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>a unlikeable person</t>
+          <t>a presumptuous person</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0.012062114663</t>
+          <t>0.010384392925</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>a weak-willed person</t>
+          <t>a unimpressive person</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0.011413822882</t>
+          <t>0.010226285085</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>a thoughtless person</t>
+          <t>a charmless person</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0.011217828840</t>
+          <t>0.009968741797</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>a deceitful person</t>
+          <t>a unpolished person</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0.010961752385</t>
+          <t>0.009597768076</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>a narcissistic person</t>
+          <t>a criminal person</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0.010825430974</t>
+          <t>0.009370841086</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>a scheming person</t>
+          <t>a meddlesome person</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0.010810657404</t>
+          <t>0.009272961877</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>a uncharitable person</t>
+          <t>a uncreative person</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0.010663392954</t>
+          <t>0.009218875319</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>a miserable person</t>
+          <t>a erratic person</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0.010116639547</t>
+          <t>0.009107233025</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>a brutal person</t>
+          <t>a pompous person</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0.009940456599</t>
+          <t>0.008931014687</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>a malicious person</t>
+          <t>a careless person</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0.009624629281</t>
+          <t>0.008211535402</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>a undisciplined person</t>
+          <t>a uncooperative person</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0.009447800927</t>
+          <t>0.007887307554</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>a perverse person</t>
+          <t>a obnoxious person</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0.009364930913</t>
+          <t>0.007580478676</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>a shallow person</t>
+          <t>a graceless person</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0.009312386625</t>
+          <t>0.007565859705</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>a insincere person</t>
+          <t>a dismissive person</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0.008139342070</t>
+          <t>0.007313150913</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>a morbid person</t>
+          <t>a prejudiced person</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0.007542349398</t>
+          <t>0.007311296184</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>a devious person</t>
+          <t>a contradictory person</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0.007388740312</t>
+          <t>0.007202944253</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>a unreliable person</t>
+          <t>a tactless person</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0.007104014978</t>
+          <t>0.007164072711</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>a sly person</t>
+          <t>a disruptive person</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0.006725291722</t>
+          <t>0.007101641037</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>a deceptive person</t>
+          <t>a unhealthy person</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0.006449369248</t>
+          <t>0.007025761995</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>a irresponsible person</t>
+          <t>a dull person</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0.006449332461</t>
+          <t>0.006934220903</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>a hateful person</t>
+          <t>a unfriendly person</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0.006242293399</t>
+          <t>0.006623649970</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>a false person</t>
+          <t>a misguided person</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0.006138170604</t>
+          <t>0.006578324828</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>a narrow-minded person</t>
+          <t>a crude person</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0.005998233333</t>
+          <t>0.006560331676</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>a unstable person</t>
+          <t>a tasteless person</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0.005836430006</t>
+          <t>0.006441793405</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>a callous person</t>
+          <t>a abrupt person</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0.005824741907</t>
+          <t>0.006362543441</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>a frightening person</t>
+          <t>a cold person</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0.005727594718</t>
+          <t>0.006257059053</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>a conceited person</t>
+          <t>a fickle person</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0.005620885640</t>
+          <t>0.006137839518</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>a uncaring person</t>
+          <t>a dirty person</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0.005504372064</t>
+          <t>0.006123935804</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>a predatory person</t>
+          <t>a resentful person</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0.005439653061</t>
+          <t>0.005880463868</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>a desperate person</t>
+          <t>a stupid person</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0.005232440773</t>
+          <t>0.005871262867</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>a monstrous person</t>
+          <t>a disturbing person</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0.005126833450</t>
+          <t>0.005752597935</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>a discouraging person</t>
+          <t>a disrespectful person</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0.004860084038</t>
+          <t>0.005527494475</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>a dishonest person</t>
+          <t>a gloomy person</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0.004624311347</t>
+          <t>0.005210458301</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>a neglectful person</t>
+          <t>a neurotic person</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0.004565513227</t>
+          <t>0.005144963507</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>a weak person</t>
+          <t>a remorseless person</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0.004416691139</t>
+          <t>0.005057224538</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>a hostile person</t>
+          <t>a unlikeable person</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0.004388376139</t>
+          <t>0.005013276823</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>a aggressive person</t>
+          <t>a weak-willed person</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0.004370358773</t>
+          <t>0.004743832629</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>a slow person</t>
+          <t>a thoughtless person</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0.004152058158</t>
+          <t>0.004662373569</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>a cruel person</t>
+          <t>a easily discouraged person</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0.003962374758</t>
+          <t>0.004659973551</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>a treacherous person</t>
+          <t>a irritable person</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0.003924631979</t>
+          <t>0.004617874511</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>a sadistic person</t>
+          <t>a deceitful person</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0.003823837033</t>
+          <t>0.004555942491</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>a vindictive person</t>
+          <t>a narcissistic person</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0.003648925805</t>
+          <t>0.004499284085</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>a foolish person</t>
+          <t>a scheming person</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0.003399979323</t>
+          <t>0.004493143875</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>a fraudulent person</t>
+          <t>a insecure person</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0.003299442120</t>
+          <t>0.004450166598</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>a insulting person</t>
+          <t>a uncharitable person</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0.003203991335</t>
+          <t>0.004431937821</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>a sloppy person</t>
+          <t>a moody person</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0.002677397570</t>
+          <t>0.004403827246</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>a venomous person</t>
+          <t>a miserable person</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0.002659898251</t>
+          <t>0.004204670899</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>a intolerant person</t>
+          <t>a brutal person</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0.002655295655</t>
+          <t>0.004131469410</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>a barbaric person</t>
+          <t>a rigid person</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0.002590670716</t>
+          <t>0.004110341892</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>a unprincipled person</t>
+          <t>a crass person</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0.002552783815</t>
+          <t>0.004102290608</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>a greedy person</t>
+          <t>a unrealistic person</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0.002274255035</t>
+          <t>0.004029149655</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>a paranoid person</t>
+          <t>a malicious person</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0.002227686346</t>
+          <t>0.004000204615</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>a grim person</t>
+          <t>a undisciplined person</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0.002174600726</t>
+          <t>0.003926711623</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>a heartless person</t>
+          <t>a perverse person</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0.001921323594</t>
+          <t>0.003892268753</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>a insensitive person</t>
+          <t>a shallow person</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>0.001911494648</t>
+          <t>0.003870429937</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>a unlovable person</t>
+          <t>a childish person</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0.001769267023</t>
+          <t>0.003667449113</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>a unappreciative person</t>
+          <t>a aimless person</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0.001692234306</t>
+          <t>0.003639880335</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>a destructive person</t>
+          <t>a insincere person</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>0.001582612516</t>
+          <t>0.003382887691</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>a ignorant person</t>
+          <t>a morbid person</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>0.001566243474</t>
+          <t>0.003134752158</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>a disloyal person</t>
+          <t>a devious person</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0.001550516812</t>
+          <t>0.003070920706</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>a cowardly person</t>
+          <t>a mistaken person</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>0.001538964105</t>
+          <t>0.003014529590</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>a irrational person</t>
+          <t>a unreliable person</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0.001467400696</t>
+          <t>0.002952583134</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>a inconsiderate person</t>
+          <t>a sly person</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>0.001058823662</t>
+          <t>0.002795177512</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>a ungrateful person</t>
+          <t>a deceptive person</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>0.000991846202</t>
+          <t>0.002680497942</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
+          <t>a irresponsible person</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>0.002680482576</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>a hateful person</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>0.002594432561</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>a false person</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>0.002551156795</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>a narrow-minded person</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>0.002492995933</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>a unstable person</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>0.002425746992</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>a callous person</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>0.002420889214</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>a frightening person</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>0.002380512888</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>a conceited person</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>0.002336162142</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>a uncaring person</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>0.002287736628</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>a predatory person</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>0.002260837937</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>a obsessive person</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>0.002212825464</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>a petty person</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>0.002207315760</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>a desperate person</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>0.002174715977</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>a abrasive person</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>0.002145811915</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>a monstrous person</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>0.002130823443</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>a envious person</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>0.002031055978</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>a discouraging person</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>0.002019956708</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>a dishonest person</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>0.001921964111</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>a neglectful person</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>0.001897526556</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>a weak person</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>0.001835672883</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>a hostile person</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>0.001823904458</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>a aggressive person</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>0.001816415926</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>a slow person</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>0.001725685550</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>a cruel person</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>0.001646849094</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>a treacherous person</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>0.001631162246</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>a sadistic person</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>0.001589269727</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>a vindictive person</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>0.001516572782</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>a foolish person</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>0.001413105289</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>a fraudulent person</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>0.001371319755</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>a insulting person</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>0.001331648440</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>a amoral person</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>0.001136326347</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>a sloppy person</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>0.001112784608</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>a venomous person</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>0.001105511445</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>a intolerant person</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>0.001103598508</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>a barbaric person</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>0.001076739049</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>a unprincipled person</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>0.001060992479</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>a gullible person</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>0.001048401464</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>a submissive person</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>0.000988991465</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>a greedy person</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>0.000945229840</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>a paranoid person</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>0.000925874861</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>a grim person</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>0.000903809618</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>a disobedient person</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>0.000898200320</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>a heartless person</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>0.000798543799</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>a insensitive person</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>0.000794458727</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>a unlovable person</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>0.000735345820</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>a unappreciative person</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>0.000703329337</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>a destructive person</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>0.000657768163</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>a ignorant person</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>0.000650964794</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>a disloyal person</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>0.000644430867</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>a cowardly person</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>0.000639626931</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>a irrational person</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>0.000609883631</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>a sneaky person</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>0.000551393954</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>a inconsiderate person</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>0.000440070144</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>a difficult person</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>0.000413219212</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>a ungrateful person</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>0.000412232854</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>a stingy person</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>0.000401868660</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>a possessive person</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>0.000319083367</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
           <t>a selfish person</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>0.000315299345</t>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>0.000131045250</t>
         </is>
       </c>
     </row>
